--- a/artfynd/A 25633-2024 artfynd.xlsx
+++ b/artfynd/A 25633-2024 artfynd.xlsx
@@ -2015,7 +2015,7 @@
         <v>126918704</v>
       </c>
       <c r="B13" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2116,7 +2116,7 @@
         <v>126918705</v>
       </c>
       <c r="B14" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2217,7 +2217,7 @@
         <v>126918706</v>
       </c>
       <c r="B15" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
